--- a/DATA/03_market_shares.xlsx
+++ b/DATA/03_market_shares.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K133"/>
+  <dimension ref="A1:K129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,16 +489,16 @@
         <v>2020</v>
       </c>
       <c r="D2" t="n">
-        <v>8.134284290249532</v>
+        <v>7.258187461772813</v>
       </c>
       <c r="E2" t="n">
-        <v>7.970343470399649</v>
+        <v>7.697022533760863</v>
       </c>
       <c r="F2" t="n">
-        <v>8.112701234554885</v>
+        <v>7.063381257202305</v>
       </c>
       <c r="G2" t="n">
-        <v>7.718842081701862</v>
+        <v>5.958006405247099</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -507,115 +507,115 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2020</v>
       </c>
       <c r="D3" t="n">
-        <v>7.736231350156567</v>
+        <v>7.054488768262901</v>
       </c>
       <c r="E3" t="n">
-        <v>7.738236197056287</v>
+        <v>6.129051666305203</v>
       </c>
       <c r="F3" t="n">
-        <v>7.762751444355417</v>
+        <v>7.681748268999867</v>
       </c>
       <c r="G3" t="n">
-        <v>7.677755053857735</v>
+        <v>8.966362722977673</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>2020</v>
       </c>
       <c r="D4" t="n">
-        <v>7.379351630134463</v>
+        <v>6.66949703261103</v>
       </c>
       <c r="E4" t="n">
-        <v>7.331049468148324</v>
+        <v>6.510171383045615</v>
       </c>
       <c r="F4" t="n">
-        <v>7.494402463838401</v>
+        <v>6.707908677626142</v>
       </c>
       <c r="G4" t="n">
-        <v>6.962718121525617</v>
+        <v>6.346950543176015</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>2020</v>
       </c>
       <c r="D5" t="n">
-        <v>6.216614477804383</v>
+        <v>6.295267202050193</v>
       </c>
       <c r="E5" t="n">
-        <v>6.091322953951014</v>
+        <v>6.02433297242134</v>
       </c>
       <c r="F5" t="n">
-        <v>6.200119660102054</v>
+        <v>6.347815125182088</v>
       </c>
       <c r="G5" t="n">
-        <v>5.899054691739974</v>
+        <v>7.093990395201902</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -627,34 +627,34 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>2020</v>
       </c>
       <c r="D6" t="n">
-        <v>5.782941284821167</v>
+        <v>5.379866000656773</v>
       </c>
       <c r="E6" t="n">
-        <v>5.823789867494925</v>
+        <v>5.505184454217783</v>
       </c>
       <c r="F6" t="n">
-        <v>5.76759715135158</v>
+        <v>5.534592433220471</v>
       </c>
       <c r="G6" t="n">
-        <v>5.936462284254776</v>
+        <v>4.963585135811927</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -666,82 +666,82 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>2020</v>
       </c>
       <c r="D7" t="n">
-        <v>5.18836748182419</v>
+        <v>5.042822327154262</v>
       </c>
       <c r="E7" t="n">
-        <v>5.401537030554524</v>
+        <v>4.250613738153008</v>
       </c>
       <c r="F7" t="n">
-        <v>5.143048512419348</v>
+        <v>4.727906638010558</v>
       </c>
       <c r="G7" t="n">
-        <v>5.906413562398623</v>
+        <v>4.778617494907245</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>2020</v>
       </c>
       <c r="D8" t="n">
-        <v>5.097082118903925</v>
+        <v>4.899615820458618</v>
       </c>
       <c r="E8" t="n">
-        <v>5.16776721384864</v>
+        <v>4.559778241599245</v>
       </c>
       <c r="F8" t="n">
-        <v>5.021563198456543</v>
+        <v>4.775520290771707</v>
       </c>
       <c r="G8" t="n">
-        <v>5.481745401472387</v>
+        <v>5.154185789036519</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
       </c>
       <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
         <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>8</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
@@ -750,235 +750,235 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2020</v>
       </c>
       <c r="D9" t="n">
-        <v>5.051303999219876</v>
+        <v>4.837383784818146</v>
       </c>
       <c r="E9" t="n">
-        <v>5.155727598278799</v>
+        <v>5.017104669729111</v>
       </c>
       <c r="F9" t="n">
-        <v>5.19149569856197</v>
+        <v>4.644576757376774</v>
       </c>
       <c r="G9" t="n">
-        <v>5.009551200875705</v>
+        <v>4.390902377848128</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>2020</v>
       </c>
       <c r="D10" t="n">
-        <v>4.624267279208608</v>
+        <v>4.751438960244097</v>
       </c>
       <c r="E10" t="n">
-        <v>4.531068401236372</v>
+        <v>4.70234384386896</v>
       </c>
       <c r="F10" t="n">
-        <v>4.499509762577489</v>
+        <v>4.380122372543605</v>
       </c>
       <c r="G10" t="n">
-        <v>4.660618083811404</v>
+        <v>3.508403942289277</v>
       </c>
       <c r="H10" t="n">
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>2020</v>
       </c>
       <c r="D11" t="n">
-        <v>4.514833194283423</v>
+        <v>4.751271860607973</v>
       </c>
       <c r="E11" t="n">
-        <v>4.454561915768991</v>
+        <v>5.001018392498532</v>
       </c>
       <c r="F11" t="n">
-        <v>4.447942584236494</v>
+        <v>4.778939943767318</v>
       </c>
       <c r="G11" t="n">
-        <v>4.504855321536655</v>
+        <v>6.824629987904387</v>
       </c>
       <c r="H11" t="n">
         <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>2020</v>
       </c>
       <c r="D12" t="n">
-        <v>4.446707767653018</v>
+        <v>4.441685755681556</v>
       </c>
       <c r="E12" t="n">
-        <v>4.387345029577789</v>
+        <v>4.051628102274796</v>
       </c>
       <c r="F12" t="n">
-        <v>4.434909121578881</v>
+        <v>4.274794132664585</v>
       </c>
       <c r="G12" t="n">
-        <v>4.305859194142339</v>
+        <v>2.446161204522388</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
         <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NMB Bank</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>2020</v>
       </c>
       <c r="D13" t="n">
-        <v>4.380613914381373</v>
+        <v>4.126503534256611</v>
       </c>
       <c r="E13" t="n">
-        <v>4.500980421358529</v>
+        <v>4.131335664882362</v>
       </c>
       <c r="F13" t="n">
-        <v>4.368990638046641</v>
+        <v>4.167338382239118</v>
       </c>
       <c r="G13" t="n">
-        <v>4.752297347433747</v>
+        <v>5.298554773875522</v>
       </c>
       <c r="H13" t="n">
         <v>12</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>12</v>
       </c>
       <c r="K13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>2020</v>
       </c>
       <c r="D14" t="n">
-        <v>4.18761444529921</v>
+        <v>4.073191865086561</v>
       </c>
       <c r="E14" t="n">
-        <v>4.245689699662831</v>
+        <v>4.514964582391368</v>
       </c>
       <c r="F14" t="n">
-        <v>4.176503262978113</v>
+        <v>3.87732659080717</v>
       </c>
       <c r="G14" t="n">
-        <v>4.380367759561166</v>
+        <v>2.373054946450536</v>
       </c>
       <c r="H14" t="n">
         <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -996,67 +996,67 @@
         <v>2020</v>
       </c>
       <c r="D15" t="n">
-        <v>4.158224350709155</v>
+        <v>4.031038267498261</v>
       </c>
       <c r="E15" t="n">
-        <v>4.074418242531678</v>
+        <v>4.48901869864216</v>
       </c>
       <c r="F15" t="n">
-        <v>4.197766652258255</v>
+        <v>3.973624471613044</v>
       </c>
       <c r="G15" t="n">
-        <v>3.823546546390014</v>
+        <v>4.611859846556745</v>
       </c>
       <c r="H15" t="n">
         <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
         <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>2020</v>
       </c>
       <c r="D16" t="n">
-        <v>4.069647752267236</v>
+        <v>3.505498524749873</v>
       </c>
       <c r="E16" t="n">
-        <v>3.987626843579958</v>
+        <v>3.642100445054348</v>
       </c>
       <c r="F16" t="n">
-        <v>4.083598658963438</v>
+        <v>3.674351106122841</v>
       </c>
       <c r="G16" t="n">
-        <v>3.801776554024842</v>
+        <v>3.161348932339329</v>
       </c>
       <c r="H16" t="n">
         <v>15</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
         <v>15</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -1074,16 +1074,16 @@
         <v>2020</v>
       </c>
       <c r="D17" t="n">
-        <v>3.552544613350958</v>
+        <v>3.340288359154795</v>
       </c>
       <c r="E17" t="n">
-        <v>3.505120633556569</v>
+        <v>3.680734171173921</v>
       </c>
       <c r="F17" t="n">
-        <v>3.521515756125332</v>
+        <v>3.554249725770711</v>
       </c>
       <c r="G17" t="n">
-        <v>3.492397366750782</v>
+        <v>3.638434350313963</v>
       </c>
       <c r="H17" t="n">
         <v>16</v>
@@ -1095,73 +1095,73 @@
         <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>2020</v>
       </c>
       <c r="D18" t="n">
-        <v>3.059684916515879</v>
+        <v>3.298043929276178</v>
       </c>
       <c r="E18" t="n">
-        <v>3.143755221713244</v>
+        <v>3.752677598458657</v>
       </c>
       <c r="F18" t="n">
-        <v>3.107387034538017</v>
+        <v>3.463197930001104</v>
       </c>
       <c r="G18" t="n">
-        <v>3.184244657919831</v>
+        <v>2.591492922376066</v>
       </c>
       <c r="H18" t="n">
         <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
         <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>2020</v>
       </c>
       <c r="D19" t="n">
-        <v>2.910296555535089</v>
+        <v>3.088600027199372</v>
       </c>
       <c r="E19" t="n">
-        <v>2.871444627057978</v>
+        <v>3.293595054922072</v>
       </c>
       <c r="F19" t="n">
-        <v>2.955670412853709</v>
+        <v>3.00157870930366</v>
       </c>
       <c r="G19" t="n">
-        <v>2.689360606125647</v>
+        <v>2.891374014606913</v>
       </c>
       <c r="H19" t="n">
         <v>18</v>
@@ -1170,127 +1170,127 @@
         <v>18</v>
       </c>
       <c r="J19" t="n">
+        <v>20</v>
+      </c>
+      <c r="K19" t="n">
         <v>18</v>
-      </c>
-      <c r="K19" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>2020</v>
       </c>
       <c r="D20" t="n">
-        <v>2.668810202290531</v>
+        <v>3.083373595474264</v>
       </c>
       <c r="E20" t="n">
-        <v>2.687661701695337</v>
+        <v>2.191030941103425</v>
       </c>
       <c r="F20" t="n">
-        <v>2.661728930333572</v>
+        <v>3.275853909043964</v>
       </c>
       <c r="G20" t="n">
-        <v>2.739646222293085</v>
+        <v>4.070906310714911</v>
       </c>
       <c r="H20" t="n">
         <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>2020</v>
       </c>
       <c r="D21" t="n">
-        <v>2.116086810484002</v>
+        <v>2.925289130368607</v>
       </c>
       <c r="E21" t="n">
-        <v>2.159831831711389</v>
+        <v>3.21757326195661</v>
       </c>
       <c r="F21" t="n">
-        <v>2.084734639227428</v>
+        <v>2.944788316759366</v>
       </c>
       <c r="G21" t="n">
-        <v>2.316817779031511</v>
+        <v>5.154185789036519</v>
       </c>
       <c r="H21" t="n">
         <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>BOKL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Bank of Kathmandu</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2020</v>
       </c>
       <c r="D22" t="n">
-        <v>2.007871669574074</v>
+        <v>2.901949468831701</v>
       </c>
       <c r="E22" t="n">
-        <v>2.076704663585272</v>
+        <v>3.085303348554842</v>
       </c>
       <c r="F22" t="n">
-        <v>2.063596444987982</v>
+        <v>3.064124192534894</v>
       </c>
       <c r="G22" t="n">
-        <v>2.069069133523642</v>
+        <v>2.992051307524578</v>
       </c>
       <c r="H22" t="n">
         <v>21</v>
       </c>
       <c r="I22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1308,22 +1308,22 @@
         <v>2020</v>
       </c>
       <c r="D23" t="n">
-        <v>1.574875667710444</v>
+        <v>2.200328550721949</v>
       </c>
       <c r="E23" t="n">
-        <v>1.575283797257887</v>
+        <v>2.459866565141169</v>
       </c>
       <c r="F23" t="n">
-        <v>1.570696980559187</v>
+        <v>2.172918175372168</v>
       </c>
       <c r="G23" t="n">
-        <v>1.586143246549763</v>
+        <v>1.647973600631717</v>
       </c>
       <c r="H23" t="n">
         <v>22</v>
       </c>
       <c r="I23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
         <v>22</v>
@@ -1347,16 +1347,16 @@
         <v>2020</v>
       </c>
       <c r="D24" t="n">
-        <v>1.141744227622897</v>
+        <v>2.044369773063467</v>
       </c>
       <c r="E24" t="n">
-        <v>1.11873316997401</v>
+        <v>2.093549669844614</v>
       </c>
       <c r="F24" t="n">
-        <v>1.131769757095264</v>
+        <v>1.913342593066543</v>
       </c>
       <c r="G24" t="n">
-        <v>1.10045778307889</v>
+        <v>1.136967206650642</v>
       </c>
       <c r="H24" t="n">
         <v>23</v>
@@ -1374,28 +1374,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2021</v>
       </c>
       <c r="D25" t="n">
-        <v>8.250655237341526</v>
+        <v>7.454804495904523</v>
       </c>
       <c r="E25" t="n">
-        <v>8.052987302155715</v>
+        <v>8.178758947393398</v>
       </c>
       <c r="F25" t="n">
-        <v>8.486463371466979</v>
+        <v>7.865688514237257</v>
       </c>
       <c r="G25" t="n">
-        <v>7.16300191204589</v>
+        <v>5.896451812162042</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -1407,34 +1407,34 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>2021</v>
       </c>
       <c r="D26" t="n">
-        <v>7.822833604172177</v>
+        <v>7.439206473696523</v>
       </c>
       <c r="E26" t="n">
-        <v>8.001498388902007</v>
+        <v>7.431297069404229</v>
       </c>
       <c r="F26" t="n">
-        <v>7.760743470124189</v>
+        <v>7.356216531937922</v>
       </c>
       <c r="G26" t="n">
-        <v>8.458652007648183</v>
+        <v>7.53609505740434</v>
       </c>
       <c r="H26" t="n">
         <v>2</v>
@@ -1446,502 +1446,502 @@
         <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>2021</v>
       </c>
       <c r="D27" t="n">
-        <v>7.284305203884962</v>
+        <v>6.676043527574668</v>
       </c>
       <c r="E27" t="n">
-        <v>7.450671344331742</v>
+        <v>6.010022615251748</v>
       </c>
       <c r="F27" t="n">
-        <v>7.270823681399357</v>
+        <v>7.230238820556472</v>
       </c>
       <c r="G27" t="n">
-        <v>7.774139579349903</v>
+        <v>6.194483234285049</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>3</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>2021</v>
       </c>
       <c r="D28" t="n">
-        <v>6.185573885651914</v>
+        <v>6.268546328056704</v>
       </c>
       <c r="E28" t="n">
-        <v>6.120085830113158</v>
+        <v>6.156658672415776</v>
       </c>
       <c r="F28" t="n">
-        <v>6.061183174825814</v>
+        <v>6.124141788111197</v>
       </c>
       <c r="G28" t="n">
-        <v>6.291108986615679</v>
+        <v>8.191793135217464</v>
       </c>
       <c r="H28" t="n">
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C29" t="n">
         <v>2021</v>
       </c>
       <c r="D29" t="n">
-        <v>5.815217512121057</v>
+        <v>4.986707901130058</v>
       </c>
       <c r="E29" t="n">
-        <v>5.637023937841649</v>
+        <v>4.695160713195757</v>
       </c>
       <c r="F29" t="n">
-        <v>5.769063257939806</v>
+        <v>4.507699401125064</v>
       </c>
       <c r="G29" t="n">
-        <v>5.429971319311664</v>
+        <v>4.90519698624952</v>
       </c>
       <c r="H29" t="n">
         <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C30" t="n">
         <v>2021</v>
       </c>
       <c r="D30" t="n">
-        <v>5.139417166662591</v>
+        <v>4.930607484084223</v>
       </c>
       <c r="E30" t="n">
-        <v>5.25679720234159</v>
+        <v>5.117778317902228</v>
       </c>
       <c r="F30" t="n">
-        <v>5.067345502556635</v>
+        <v>4.958079954786997</v>
       </c>
       <c r="G30" t="n">
-        <v>5.628824091778203</v>
+        <v>5.165305031686646</v>
       </c>
       <c r="H30" t="n">
         <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C31" t="n">
         <v>2021</v>
       </c>
       <c r="D31" t="n">
-        <v>5.078950819963675</v>
+        <v>4.908816211874354</v>
       </c>
       <c r="E31" t="n">
-        <v>4.99122343340902</v>
+        <v>5.033970695385413</v>
       </c>
       <c r="F31" t="n">
-        <v>4.97681655181491</v>
+        <v>4.783616244873868</v>
       </c>
       <c r="G31" t="n">
-        <v>5.071940726577438</v>
+        <v>6.438669251342607</v>
       </c>
       <c r="H31" t="n">
         <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
         <v>2021</v>
       </c>
       <c r="D32" t="n">
-        <v>5.055831334461149</v>
+        <v>4.795003371096867</v>
       </c>
       <c r="E32" t="n">
-        <v>5.171302363062615</v>
+        <v>4.210340533100512</v>
       </c>
       <c r="F32" t="n">
-        <v>4.92338945262362</v>
+        <v>4.461772407924841</v>
       </c>
       <c r="G32" t="n">
-        <v>5.679015296367113</v>
+        <v>5.357816829366879</v>
       </c>
       <c r="H32" t="n">
         <v>8</v>
       </c>
       <c r="I32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>2021</v>
       </c>
       <c r="D33" t="n">
-        <v>4.618672985992704</v>
+        <v>4.790585589781418</v>
       </c>
       <c r="E33" t="n">
-        <v>4.662405359436188</v>
+        <v>4.682234372148189</v>
       </c>
       <c r="F33" t="n">
-        <v>4.666347305531813</v>
+        <v>4.461814884453688</v>
       </c>
       <c r="G33" t="n">
-        <v>4.629541108986616</v>
+        <v>6.382453635234291</v>
       </c>
       <c r="H33" t="n">
         <v>9</v>
       </c>
       <c r="I33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" t="n">
         <v>9</v>
       </c>
-      <c r="J33" t="n">
-        <v>10</v>
-      </c>
       <c r="K33" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C34" t="n">
         <v>2021</v>
       </c>
       <c r="D34" t="n">
-        <v>4.557762033803355</v>
+        <v>4.641406162240464</v>
       </c>
       <c r="E34" t="n">
-        <v>4.539976892258431</v>
+        <v>4.200929326069776</v>
       </c>
       <c r="F34" t="n">
-        <v>4.688025004661747</v>
+        <v>4.517598076599196</v>
       </c>
       <c r="G34" t="n">
-        <v>4.209130019120458</v>
+        <v>3.113606929266751</v>
       </c>
       <c r="H34" t="n">
         <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>2021</v>
       </c>
       <c r="D35" t="n">
-        <v>4.429604501185985</v>
+        <v>4.558204650027005</v>
       </c>
       <c r="E35" t="n">
-        <v>4.501158834930402</v>
+        <v>4.202653936753604</v>
       </c>
       <c r="F35" t="n">
-        <v>4.394446558274924</v>
+        <v>4.390709997289806</v>
       </c>
       <c r="G35" t="n">
-        <v>4.70793499043977</v>
+        <v>3.20419965210368</v>
       </c>
       <c r="H35" t="n">
         <v>11</v>
       </c>
       <c r="I35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J35" t="n">
         <v>11</v>
       </c>
-      <c r="J35" t="n">
-        <v>12</v>
-      </c>
       <c r="K35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NMB Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C36" t="n">
         <v>2021</v>
       </c>
       <c r="D36" t="n">
-        <v>4.346463274474976</v>
+        <v>4.103503975106189</v>
       </c>
       <c r="E36" t="n">
-        <v>4.445731642506735</v>
+        <v>4.209199808997579</v>
       </c>
       <c r="F36" t="n">
-        <v>4.470687873090291</v>
+        <v>4.224071834200943</v>
       </c>
       <c r="G36" t="n">
-        <v>4.334608030592734</v>
+        <v>5.913586085884146</v>
       </c>
       <c r="H36" t="n">
         <v>12</v>
       </c>
       <c r="I36" t="n">
+        <v>11</v>
+      </c>
+      <c r="J36" t="n">
         <v>12</v>
       </c>
-      <c r="J36" t="n">
-        <v>11</v>
-      </c>
       <c r="K36" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>2021</v>
       </c>
       <c r="D37" t="n">
-        <v>4.149503042213068</v>
+        <v>4.08725684292477</v>
       </c>
       <c r="E37" t="n">
-        <v>4.022350284162447</v>
+        <v>4.287366925470403</v>
       </c>
       <c r="F37" t="n">
-        <v>4.268098396026154</v>
+        <v>3.996581795885553</v>
       </c>
       <c r="G37" t="n">
-        <v>3.526051625239006</v>
+        <v>3.56568397596208</v>
       </c>
       <c r="H37" t="n">
         <v>13</v>
       </c>
       <c r="I37" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J37" t="n">
         <v>13</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C38" t="n">
         <v>2021</v>
       </c>
       <c r="D38" t="n">
-        <v>4.144723533190912</v>
+        <v>3.84406910510923</v>
       </c>
       <c r="E38" t="n">
-        <v>4.156260692799481</v>
+        <v>4.106915813827459</v>
       </c>
       <c r="F38" t="n">
-        <v>4.263181609193163</v>
+        <v>3.864571321239309</v>
       </c>
       <c r="G38" t="n">
-        <v>3.903919694072658</v>
+        <v>5.425467356765975</v>
       </c>
       <c r="H38" t="n">
         <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J38" t="n">
         <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2021</v>
       </c>
       <c r="D39" t="n">
-        <v>4.033461009210003</v>
+        <v>3.625217822538024</v>
       </c>
       <c r="E39" t="n">
-        <v>3.909864114209976</v>
+        <v>3.798036392537534</v>
       </c>
       <c r="F39" t="n">
-        <v>4.02599602884901</v>
+        <v>3.854084825414356</v>
       </c>
       <c r="G39" t="n">
-        <v>3.709847036328872</v>
+        <v>3.264630987089768</v>
       </c>
       <c r="H39" t="n">
         <v>15</v>
@@ -1971,16 +1971,16 @@
         <v>2021</v>
       </c>
       <c r="D40" t="n">
-        <v>3.536836676396117</v>
+        <v>3.462004137725035</v>
       </c>
       <c r="E40" t="n">
-        <v>3.428457785332933</v>
+        <v>3.702033686288522</v>
       </c>
       <c r="F40" t="n">
-        <v>3.487238502775901</v>
+        <v>3.519409788248009</v>
       </c>
       <c r="G40" t="n">
-        <v>3.351816443594646</v>
+        <v>4.193681343037569</v>
       </c>
       <c r="H40" t="n">
         <v>16</v>
@@ -1989,37 +1989,37 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K40" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C41" t="n">
         <v>2021</v>
       </c>
       <c r="D41" t="n">
-        <v>3.103457474596353</v>
+        <v>3.407365402626646</v>
       </c>
       <c r="E41" t="n">
-        <v>3.153589677559263</v>
+        <v>3.646541142949215</v>
       </c>
       <c r="F41" t="n">
-        <v>3.022159717423033</v>
+        <v>3.606886499840219</v>
       </c>
       <c r="G41" t="n">
-        <v>3.428776290630975</v>
+        <v>2.908429881739135</v>
       </c>
       <c r="H41" t="n">
         <v>17</v>
@@ -2028,10 +2028,10 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -2049,64 +2049,64 @@
         <v>2021</v>
       </c>
       <c r="D42" t="n">
-        <v>2.879709761535845</v>
+        <v>2.967917950621377</v>
       </c>
       <c r="E42" t="n">
-        <v>2.926227619576856</v>
+        <v>3.014299550256853</v>
       </c>
       <c r="F42" t="n">
-        <v>2.856853393350063</v>
+        <v>2.91138157138038</v>
       </c>
       <c r="G42" t="n">
-        <v>3.060707456978967</v>
+        <v>1.743244988993898</v>
       </c>
       <c r="H42" t="n">
         <v>18</v>
       </c>
       <c r="I42" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>2021</v>
       </c>
       <c r="D43" t="n">
-        <v>2.695976542614325</v>
+        <v>2.966941270551882</v>
       </c>
       <c r="E43" t="n">
-        <v>2.757550379656056</v>
+        <v>3.124342272597505</v>
       </c>
       <c r="F43" t="n">
-        <v>2.641762234850364</v>
+        <v>3.140673162603137</v>
       </c>
       <c r="G43" t="n">
-        <v>2.990439770554493</v>
+        <v>2.851056299930486</v>
       </c>
       <c r="H43" t="n">
         <v>19</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K43" t="n">
         <v>19</v>
@@ -2120,35 +2120,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Bank of Kathmandu</t>
         </is>
       </c>
       <c r="C44" t="n">
         <v>2021</v>
       </c>
       <c r="D44" t="n">
-        <v>2.141220041926298</v>
+        <v>2.842423499336834</v>
       </c>
       <c r="E44" t="n">
-        <v>2.104235935795765</v>
+        <v>3.015151440156563</v>
       </c>
       <c r="F44" t="n">
-        <v>2.111193039518383</v>
+        <v>2.833963575861314</v>
       </c>
       <c r="G44" t="n">
-        <v>2.108269598470363</v>
+        <v>3.123630569860252</v>
       </c>
       <c r="H44" t="n">
         <v>20</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
         <v>20</v>
       </c>
       <c r="K44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
@@ -2166,28 +2166,28 @@
         <v>2021</v>
       </c>
       <c r="D45" t="n">
-        <v>2.009061059895028</v>
+        <v>2.47107078479866</v>
       </c>
       <c r="E45" t="n">
-        <v>1.987790680670177</v>
+        <v>2.222186826991434</v>
       </c>
       <c r="F45" t="n">
-        <v>2.029796810604586</v>
+        <v>2.399628462460889</v>
       </c>
       <c r="G45" t="n">
-        <v>1.902724665391969</v>
+        <v>2.530951156644896</v>
       </c>
       <c r="H45" t="n">
         <v>21</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -2205,25 +2205,25 @@
         <v>2021</v>
       </c>
       <c r="D46" t="n">
-        <v>1.567012051031818</v>
+        <v>2.404080223454234</v>
       </c>
       <c r="E46" t="n">
-        <v>1.550421743628667</v>
+        <v>2.496769907099976</v>
       </c>
       <c r="F46" t="n">
-        <v>1.592725038857363</v>
+        <v>2.562201484718013</v>
       </c>
       <c r="G46" t="n">
-        <v>1.461998087954111</v>
+        <v>1.138642147707934</v>
       </c>
       <c r="H46" t="n">
         <v>22</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
         <v>22</v>
@@ -2244,25 +2244,25 @@
         <v>2021</v>
       </c>
       <c r="D47" t="n">
-        <v>1.153751247674157</v>
+        <v>2.368216789740308</v>
       </c>
       <c r="E47" t="n">
-        <v>1.17238855531912</v>
+        <v>2.457351033806324</v>
       </c>
       <c r="F47" t="n">
-        <v>1.165660024241897</v>
+        <v>2.428969056251577</v>
       </c>
       <c r="G47" t="n">
-        <v>1.177581261950287</v>
+        <v>0.9549236520645985</v>
       </c>
       <c r="H47" t="n">
         <v>23</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K47" t="n">
         <v>23</v>
@@ -2271,28 +2271,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>2022</v>
       </c>
       <c r="D48" t="n">
-        <v>8.336857913163048</v>
+        <v>8.448195174951127</v>
       </c>
       <c r="E48" t="n">
-        <v>8.512331479920714</v>
+        <v>9.084992979554004</v>
       </c>
       <c r="F48" t="n">
-        <v>8.310363680123265</v>
+        <v>8.722153414966785</v>
       </c>
       <c r="G48" t="n">
-        <v>8.927757622879993</v>
+        <v>7.156455593695489</v>
       </c>
       <c r="H48" t="n">
         <v>1</v>
@@ -2304,34 +2304,34 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>2022</v>
       </c>
       <c r="D49" t="n">
-        <v>7.886984891197618</v>
+        <v>7.255258414047162</v>
       </c>
       <c r="E49" t="n">
-        <v>7.839664756945459</v>
+        <v>8.135753157481783</v>
       </c>
       <c r="F49" t="n">
-        <v>7.909858877005588</v>
+        <v>7.40516623643082</v>
       </c>
       <c r="G49" t="n">
-        <v>7.689279536362938</v>
+        <v>8.338879448256009</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
@@ -2340,37 +2340,37 @@
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>2022</v>
       </c>
       <c r="D50" t="n">
-        <v>7.213898831205853</v>
+        <v>7.215667909913837</v>
       </c>
       <c r="E50" t="n">
-        <v>7.121838613808894</v>
+        <v>7.639738520907516</v>
       </c>
       <c r="F50" t="n">
-        <v>7.103279657420987</v>
+        <v>7.751115534453773</v>
       </c>
       <c r="G50" t="n">
-        <v>7.207903260846484</v>
+        <v>7.087363164537508</v>
       </c>
       <c r="H50" t="n">
         <v>3</v>
@@ -2379,37 +2379,37 @@
         <v>3</v>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>2022</v>
       </c>
       <c r="D51" t="n">
-        <v>6.162580327813873</v>
+        <v>6.645629689435377</v>
       </c>
       <c r="E51" t="n">
-        <v>6.292288135746969</v>
+        <v>6.86105427809821</v>
       </c>
       <c r="F51" t="n">
-        <v>6.068081286547614</v>
+        <v>6.901962615000827</v>
       </c>
       <c r="G51" t="n">
-        <v>6.782390808277645</v>
+        <v>7.21833443022539</v>
       </c>
       <c r="H51" t="n">
         <v>4</v>
@@ -2421,34 +2421,34 @@
         <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>2022</v>
       </c>
       <c r="D52" t="n">
-        <v>5.839126376216446</v>
+        <v>5.319175745336397</v>
       </c>
       <c r="E52" t="n">
-        <v>5.922543808316429</v>
+        <v>5.404511580102118</v>
       </c>
       <c r="F52" t="n">
-        <v>5.927044814798692</v>
+        <v>5.121458642160536</v>
       </c>
       <c r="G52" t="n">
-        <v>5.874685357634641</v>
+        <v>4.880457822678796</v>
       </c>
       <c r="H52" t="n">
         <v>5</v>
@@ -2457,85 +2457,85 @@
         <v>5</v>
       </c>
       <c r="J52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K52" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>2022</v>
       </c>
       <c r="D53" t="n">
-        <v>5.103156843491886</v>
+        <v>5.233668321893503</v>
       </c>
       <c r="E53" t="n">
-        <v>4.969017845857861</v>
+        <v>5.189439767807203</v>
       </c>
       <c r="F53" t="n">
-        <v>5.148975039389329</v>
+        <v>5.242456474899095</v>
       </c>
       <c r="G53" t="n">
-        <v>4.589000707281735</v>
+        <v>4.915466447041637</v>
       </c>
       <c r="H53" t="n">
         <v>6</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2022</v>
       </c>
       <c r="D54" t="n">
-        <v>5.065519920552554</v>
+        <v>5.134514572591884</v>
       </c>
       <c r="E54" t="n">
-        <v>4.966624058939368</v>
+        <v>5.294386106272437</v>
       </c>
       <c r="F54" t="n">
-        <v>4.987843565755707</v>
+        <v>4.941425333941115</v>
       </c>
       <c r="G54" t="n">
-        <v>4.958485992391412</v>
+        <v>5.53393532921727</v>
       </c>
       <c r="H54" t="n">
         <v>7</v>
       </c>
       <c r="I54" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" t="n">
         <v>7</v>
-      </c>
-      <c r="J54" t="n">
-        <v>8</v>
       </c>
       <c r="K54" t="n">
         <v>6</v>
@@ -2544,67 +2544,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>2022</v>
       </c>
       <c r="D55" t="n">
-        <v>5.059184992929103</v>
+        <v>4.954080132602693</v>
       </c>
       <c r="E55" t="n">
-        <v>4.960410292054099</v>
+        <v>5.244955535319248</v>
       </c>
       <c r="F55" t="n">
-        <v>5.012357565462436</v>
+        <v>4.454097245466562</v>
       </c>
       <c r="G55" t="n">
-        <v>4.877140425643129</v>
+        <v>3.742610271281527</v>
       </c>
       <c r="H55" t="n">
         <v>8</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J55" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>2022</v>
       </c>
       <c r="D56" t="n">
-        <v>4.614528970182986</v>
+        <v>4.919156863890914</v>
       </c>
       <c r="E56" t="n">
-        <v>4.61804584741972</v>
+        <v>4.987767916643653</v>
       </c>
       <c r="F56" t="n">
-        <v>4.571816777976639</v>
+        <v>4.940729106650819</v>
       </c>
       <c r="G56" t="n">
-        <v>4.729313642696948</v>
+        <v>6.385626891466202</v>
       </c>
       <c r="H56" t="n">
         <v>9</v>
@@ -2613,232 +2613,228 @@
         <v>9</v>
       </c>
       <c r="J56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K56" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>2022</v>
       </c>
       <c r="D57" t="n">
-        <v>4.589561902490559</v>
+        <v>4.683797033894917</v>
       </c>
       <c r="E57" t="n">
-        <v>4.593059751542052</v>
+        <v>4.39961920372431</v>
       </c>
       <c r="F57" t="n">
-        <v>4.6307699688079</v>
+        <v>4.776594592436859</v>
       </c>
       <c r="G57" t="n">
-        <v>4.499487914956314</v>
+        <v>3.198227843929467</v>
       </c>
       <c r="H57" t="n">
         <v>10</v>
       </c>
       <c r="I57" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J57" t="n">
         <v>9</v>
       </c>
       <c r="K57" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>2022</v>
       </c>
       <c r="D58" t="n">
-        <v>4.416935124751494</v>
+        <v>4.535453283572377</v>
       </c>
       <c r="E58" t="n">
-        <v>4.450168310937903</v>
+        <v>4.402613987151127</v>
       </c>
       <c r="F58" t="n">
-        <v>4.429745205251463</v>
+        <v>4.618499662808354</v>
       </c>
       <c r="G58" t="n">
-        <v>4.485276942452096</v>
+        <v>4.169086611202155</v>
       </c>
       <c r="H58" t="n">
         <v>11</v>
       </c>
       <c r="I58" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J58" t="n">
         <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NMB Bank</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>2022</v>
       </c>
       <c r="D59" t="n">
-        <v>4.321165924796956</v>
-      </c>
-      <c r="E59" t="n">
-        <v>4.295239901797285</v>
-      </c>
+        <v>4.352429356004843</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="n">
-        <v>4.307433415714082</v>
+        <v>4.503004806294408</v>
       </c>
       <c r="G59" t="n">
-        <v>4.276849345723559</v>
+        <v>3.980995126032729</v>
       </c>
       <c r="H59" t="n">
         <v>12</v>
       </c>
-      <c r="I59" t="n">
-        <v>12</v>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
         <v>12</v>
       </c>
       <c r="K59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>2022</v>
       </c>
       <c r="D60" t="n">
-        <v>4.143042665737544</v>
+        <v>4.268356936907701</v>
       </c>
       <c r="E60" t="n">
-        <v>4.2862745398436</v>
+        <v>4.793868400034563</v>
       </c>
       <c r="F60" t="n">
-        <v>4.029147537494778</v>
+        <v>4.726208751774892</v>
       </c>
       <c r="G60" t="n">
-        <v>4.850678614773204</v>
+        <v>4.33792503446214</v>
       </c>
       <c r="H60" t="n">
         <v>13</v>
       </c>
       <c r="I60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>2022</v>
       </c>
       <c r="D61" t="n">
-        <v>4.112951759526148</v>
+        <v>4.233210498960268</v>
       </c>
       <c r="E61" t="n">
-        <v>4.032651555941339</v>
+        <v>4.450228198956403</v>
       </c>
       <c r="F61" t="n">
-        <v>4.149880628169034</v>
+        <v>4.283331193049364</v>
       </c>
       <c r="G61" t="n">
-        <v>3.781915475749057</v>
+        <v>4.68688467970808</v>
       </c>
       <c r="H61" t="n">
         <v>14</v>
       </c>
       <c r="I61" t="n">
+        <v>11</v>
+      </c>
+      <c r="J61" t="n">
         <v>14</v>
       </c>
-      <c r="J61" t="n">
-        <v>13</v>
-      </c>
       <c r="K61" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C62" t="n">
         <v>2022</v>
       </c>
       <c r="D62" t="n">
-        <v>4.006655400432638</v>
+        <v>3.912256312149148</v>
       </c>
       <c r="E62" t="n">
-        <v>3.928431113061529</v>
+        <v>4.074680359904333</v>
       </c>
       <c r="F62" t="n">
-        <v>4.066981950421064</v>
+        <v>4.085428853150826</v>
       </c>
       <c r="G62" t="n">
-        <v>3.624778055644941</v>
+        <v>3.372413405780895</v>
       </c>
       <c r="H62" t="n">
         <v>15</v>
@@ -2847,10 +2843,10 @@
         <v>15</v>
       </c>
       <c r="J62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K62" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="63">
@@ -2868,25 +2864,25 @@
         <v>2022</v>
       </c>
       <c r="D63" t="n">
-        <v>3.525200901050294</v>
+        <v>3.873990334534367</v>
       </c>
       <c r="E63" t="n">
-        <v>3.527887567204937</v>
+        <v>4.13138605146996</v>
       </c>
       <c r="F63" t="n">
-        <v>3.578278390158414</v>
+        <v>4.211547860051577</v>
       </c>
       <c r="G63" t="n">
-        <v>3.403772931527614</v>
+        <v>3.519560606452954</v>
       </c>
       <c r="H63" t="n">
         <v>16</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J63" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
         <v>16</v>
@@ -2895,145 +2891,145 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C64" t="n">
         <v>2022</v>
       </c>
       <c r="D64" t="n">
-        <v>3.135882334309036</v>
+        <v>3.59661290919566</v>
       </c>
       <c r="E64" t="n">
-        <v>3.074658031160151</v>
+        <v>3.969864150468355</v>
       </c>
       <c r="F64" t="n">
-        <v>3.164038680432438</v>
+        <v>3.877538164899402</v>
       </c>
       <c r="G64" t="n">
-        <v>2.883520662263987</v>
+        <v>2.836102131019693</v>
       </c>
       <c r="H64" t="n">
         <v>17</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J64" t="n">
         <v>17</v>
       </c>
       <c r="K64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>2022</v>
       </c>
       <c r="D65" t="n">
-        <v>2.857052358176808</v>
+        <v>3.489085987011917</v>
       </c>
       <c r="E65" t="n">
-        <v>2.955825408974715</v>
+        <v>3.836321806510983</v>
       </c>
       <c r="F65" t="n">
-        <v>2.917435499052984</v>
+        <v>3.730780991893417</v>
       </c>
       <c r="G65" t="n">
-        <v>3.006029045921042</v>
+        <v>3.298764138389328</v>
       </c>
       <c r="H65" t="n">
         <v>18</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
         <v>18</v>
       </c>
       <c r="K65" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C66" t="n">
         <v>2022</v>
       </c>
       <c r="D66" t="n">
-        <v>2.716100218555003</v>
+        <v>3.08095895872881</v>
       </c>
       <c r="E66" t="n">
-        <v>2.810000949451485</v>
+        <v>3.189493980166042</v>
       </c>
       <c r="F66" t="n">
-        <v>2.756994847733928</v>
+        <v>3.200672624008735</v>
       </c>
       <c r="G66" t="n">
-        <v>2.897894979279748</v>
+        <v>2.754802083568041</v>
       </c>
       <c r="H66" t="n">
         <v>19</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
         <v>19</v>
       </c>
       <c r="K66" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C67" t="n">
         <v>2022</v>
       </c>
       <c r="D67" t="n">
-        <v>2.159837676795719</v>
+        <v>2.482344410649924</v>
       </c>
       <c r="E67" t="n">
-        <v>2.132274516863246</v>
+        <v>2.396716460862513</v>
       </c>
       <c r="F67" t="n">
-        <v>2.205485346616812</v>
+        <v>2.505827895661838</v>
       </c>
       <c r="G67" t="n">
-        <v>1.965687851905332</v>
+        <v>3.793324013394078</v>
       </c>
       <c r="H67" t="n">
         <v>20</v>
@@ -3045,514 +3041,494 @@
         <v>20</v>
       </c>
       <c r="K67" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>CIVIL</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>CIVIL</t>
         </is>
       </c>
       <c r="C68" t="n">
         <v>2022</v>
       </c>
       <c r="D68" t="n">
-        <v>2.009942109940806</v>
+        <v>2.366157153727178</v>
       </c>
       <c r="E68" t="n">
-        <v>1.997882279707601</v>
-      </c>
-      <c r="F68" t="n">
-        <v>2.027989311597149</v>
-      </c>
+        <v>2.512607558565243</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>1.929752059365929</v>
+        <v>0.8874568571671666</v>
       </c>
       <c r="H68" t="n">
         <v>21</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
-      </c>
-      <c r="J68" t="n">
-        <v>21</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CCBL</t>
+          <t>BOKL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Century Commercial Bank</t>
+          <t>BOKL</t>
         </is>
       </c>
       <c r="C69" t="n">
         <v>2022</v>
       </c>
-      <c r="D69" t="n">
-        <v>1.561187016379515</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1.572934706160892</v>
-      </c>
-      <c r="F69" t="n">
-        <v>1.537247259258729</v>
-      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>1.654843246439498</v>
-      </c>
-      <c r="H69" t="n">
-        <v>22</v>
-      </c>
-      <c r="I69" t="n">
-        <v>22</v>
-      </c>
-      <c r="J69" t="n">
-        <v>22</v>
-      </c>
+        <v>3.905328070493447</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Civil Bank</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D70" t="n">
-        <v>1.162645540304114</v>
+        <v>8.524906503767101</v>
       </c>
       <c r="E70" t="n">
-        <v>1.139946528343747</v>
+        <v>9.358269077376081</v>
       </c>
       <c r="F70" t="n">
-        <v>1.158950694810964</v>
+        <v>8.518976725234989</v>
       </c>
       <c r="G70" t="n">
-        <v>1.103555519982751</v>
+        <v>11.83282639098053</v>
       </c>
       <c r="H70" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C71" t="n">
         <v>2023</v>
       </c>
       <c r="D71" t="n">
-        <v>8.387221015534859</v>
+        <v>7.785824744381019</v>
       </c>
       <c r="E71" t="n">
-        <v>8.280161459843876</v>
+        <v>8.417584081420992</v>
       </c>
       <c r="F71" t="n">
-        <v>8.146070730392987</v>
+        <v>7.929858609334234</v>
       </c>
       <c r="G71" t="n">
-        <v>8.672671033478894</v>
+        <v>11.32125297483954</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C72" t="n">
         <v>2023</v>
       </c>
       <c r="D72" t="n">
-        <v>7.924464677120216</v>
+        <v>7.219236562574221</v>
       </c>
       <c r="E72" t="n">
-        <v>7.877640578594358</v>
+        <v>7.921729267188344</v>
       </c>
       <c r="F72" t="n">
-        <v>7.98524284769467</v>
+        <v>7.082026642011773</v>
       </c>
       <c r="G72" t="n">
-        <v>7.624029597282872</v>
+        <v>6.576869995093195</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C73" t="n">
         <v>2023</v>
       </c>
       <c r="D73" t="n">
-        <v>7.17276457033665</v>
+        <v>6.375231719005018</v>
       </c>
       <c r="E73" t="n">
-        <v>7.1303815528239</v>
+        <v>5.77849158550893</v>
       </c>
       <c r="F73" t="n">
-        <v>7.314859091575726</v>
+        <v>6.427415833178284</v>
       </c>
       <c r="G73" t="n">
-        <v>6.678038573508006</v>
+        <v>6.354685009919668</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C74" t="n">
         <v>2023</v>
       </c>
       <c r="D74" t="n">
-        <v>6.149146557965624</v>
+        <v>6.156852595606144</v>
       </c>
       <c r="E74" t="n">
-        <v>6.154969791328482</v>
+        <v>7.135548117337335</v>
       </c>
       <c r="F74" t="n">
-        <v>6.233635752901264</v>
+        <v>6.315357112809425</v>
       </c>
       <c r="G74" t="n">
-        <v>5.950994662785056</v>
+        <v>0.9154657718462458</v>
       </c>
       <c r="H74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I74" t="n">
         <v>4</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C75" t="n">
         <v>2023</v>
       </c>
       <c r="D75" t="n">
-        <v>5.853094905134537</v>
+        <v>5.890927868770122</v>
       </c>
       <c r="E75" t="n">
-        <v>5.818508988712806</v>
+        <v>6.907948350715111</v>
       </c>
       <c r="F75" t="n">
-        <v>5.969046392201529</v>
+        <v>6.221857183203184</v>
       </c>
       <c r="G75" t="n">
-        <v>5.449569383794275</v>
+        <v>7.856492892201573</v>
       </c>
       <c r="H75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I75" t="n">
         <v>5</v>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C76" t="n">
         <v>2023</v>
       </c>
       <c r="D76" t="n">
-        <v>5.08197209080901</v>
+        <v>5.85171556041433</v>
       </c>
       <c r="E76" t="n">
-        <v>5.086784711414055</v>
+        <v>6.301183166142052</v>
       </c>
       <c r="F76" t="n">
-        <v>4.997552863486869</v>
+        <v>5.919635600273492</v>
       </c>
       <c r="G76" t="n">
-        <v>5.312954876273653</v>
+        <v>4.039347776594677</v>
       </c>
       <c r="H76" t="n">
+        <v>7</v>
+      </c>
+      <c r="I76" t="n">
         <v>6</v>
-      </c>
-      <c r="I76" t="n">
-        <v>7</v>
       </c>
       <c r="J76" t="n">
         <v>7</v>
       </c>
       <c r="K76" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C77" t="n">
         <v>2023</v>
       </c>
       <c r="D77" t="n">
-        <v>5.061144336338481</v>
+        <v>5.630222615490124</v>
       </c>
       <c r="E77" t="n">
-        <v>5.135333633541856</v>
+        <v>5.952523826184451</v>
       </c>
       <c r="F77" t="n">
-        <v>4.915625767364133</v>
+        <v>5.776710970800681</v>
       </c>
       <c r="G77" t="n">
-        <v>5.662906356137797</v>
+        <v>0.4953116670272533</v>
       </c>
       <c r="H77" t="n">
+        <v>8</v>
+      </c>
+      <c r="I77" t="n">
         <v>7</v>
-      </c>
-      <c r="I77" t="n">
-        <v>6</v>
       </c>
       <c r="J77" t="n">
         <v>8</v>
       </c>
       <c r="K77" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C78" t="n">
         <v>2023</v>
       </c>
       <c r="D78" t="n">
-        <v>5.057673043926727</v>
-      </c>
-      <c r="E78" t="n">
-        <v>5.027787118370794</v>
-      </c>
+        <v>5.378083486035309</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>5.096463817499246</v>
+        <v>5.501355633381499</v>
       </c>
       <c r="G78" t="n">
-        <v>4.865963124696749</v>
+        <v>2.762411603252915</v>
       </c>
       <c r="H78" t="n">
-        <v>8</v>
-      </c>
-      <c r="I78" t="n">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K78" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>2023</v>
       </c>
       <c r="D79" t="n">
-        <v>4.612107867932201</v>
+        <v>4.801151980318409</v>
       </c>
       <c r="E79" t="n">
-        <v>4.584856398997253</v>
+        <v>4.53914155649432</v>
       </c>
       <c r="F79" t="n">
-        <v>4.563490168146415</v>
+        <v>4.885959951473946</v>
       </c>
       <c r="G79" t="n">
-        <v>4.652171276079573</v>
+        <v>6.076202556346961</v>
       </c>
       <c r="H79" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J79" t="n">
         <v>10</v>
       </c>
       <c r="K79" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C80" t="n">
         <v>2023</v>
       </c>
       <c r="D80" t="n">
-        <v>4.608140676604481</v>
+        <v>4.656205004055354</v>
       </c>
       <c r="E80" t="n">
-        <v>4.549319585269812</v>
+        <v>4.805527121116441</v>
       </c>
       <c r="F80" t="n">
-        <v>4.615511385707006</v>
+        <v>4.202378158089693</v>
       </c>
       <c r="G80" t="n">
-        <v>4.407296215429403</v>
+        <v>5.696119522441922</v>
       </c>
       <c r="H80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J80" t="n">
+        <v>12</v>
+      </c>
+      <c r="K80" t="n">
         <v>9</v>
-      </c>
-      <c r="K80" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="81">
@@ -3570,220 +3546,220 @@
         <v>2023</v>
       </c>
       <c r="D81" t="n">
-        <v>4.40953316076051</v>
+        <v>4.627093806524527</v>
       </c>
       <c r="E81" t="n">
-        <v>4.353247215735181</v>
+        <v>4.6777639488687</v>
       </c>
       <c r="F81" t="n">
-        <v>4.363051345234731</v>
+        <v>4.4691418919985</v>
       </c>
       <c r="G81" t="n">
-        <v>4.354227316836487</v>
+        <v>5.597523830532777</v>
       </c>
       <c r="H81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I81" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J81" t="n">
         <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NMB Bank</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C82" t="n">
         <v>2023</v>
       </c>
       <c r="D82" t="n">
-        <v>4.306386186239797</v>
+        <v>4.298529572252646</v>
       </c>
       <c r="E82" t="n">
-        <v>4.369511784604887</v>
+        <v>4.586972764297014</v>
       </c>
       <c r="F82" t="n">
-        <v>4.3132737709591</v>
+        <v>3.986207690828754</v>
       </c>
       <c r="G82" t="n">
-        <v>4.484170305676856</v>
+        <v>2.339234934196479</v>
       </c>
       <c r="H82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I82" t="n">
         <v>11</v>
       </c>
       <c r="J82" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K82" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>2023</v>
       </c>
       <c r="D83" t="n">
-        <v>4.139268251559603</v>
+        <v>4.046438820695262</v>
       </c>
       <c r="E83" t="n">
-        <v>4.11480899874897</v>
+        <v>4.054172146335523</v>
       </c>
       <c r="F83" t="n">
-        <v>4.246395942272784</v>
+        <v>3.956657818117008</v>
       </c>
       <c r="G83" t="n">
-        <v>3.78957423580786</v>
+        <v>5.942820861985829</v>
       </c>
       <c r="H83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J83" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K83" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>2023</v>
       </c>
       <c r="D84" t="n">
-        <v>4.094389399664773</v>
+        <v>3.572971619485081</v>
       </c>
       <c r="E84" t="n">
-        <v>4.098267914076295</v>
+        <v>4.05682384297014</v>
       </c>
       <c r="F84" t="n">
-        <v>3.976667073117967</v>
+        <v>3.478085560221706</v>
       </c>
       <c r="G84" t="n">
-        <v>4.407447840853955</v>
+        <v>1.816896947174769</v>
       </c>
       <c r="H84" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J84" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K84" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>2023</v>
       </c>
       <c r="D85" t="n">
-        <v>3.990994475686076</v>
+        <v>3.489081756554598</v>
       </c>
       <c r="E85" t="n">
-        <v>3.967412476628748</v>
+        <v>3.80989396797866</v>
       </c>
       <c r="F85" t="n">
-        <v>4.045830688657207</v>
+        <v>3.511799950766731</v>
       </c>
       <c r="G85" t="n">
-        <v>3.777595827268317</v>
+        <v>4.605946002508552</v>
       </c>
       <c r="H85" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I85" t="n">
         <v>15</v>
       </c>
       <c r="J85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K85" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>2023</v>
       </c>
       <c r="D86" t="n">
-        <v>3.51840280877146</v>
+        <v>3.218709499134616</v>
       </c>
       <c r="E86" t="n">
-        <v>3.666463555987786</v>
+        <v>3.554712590632366</v>
       </c>
       <c r="F86" t="n">
-        <v>3.502672343712986</v>
+        <v>3.373859714213326</v>
       </c>
       <c r="G86" t="n">
-        <v>4.017012372634643</v>
+        <v>3.29434755741458</v>
       </c>
       <c r="H86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I86" t="n">
         <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K86" t="n">
         <v>14</v>
@@ -3792,40 +3768,40 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>2023</v>
       </c>
       <c r="D87" t="n">
-        <v>3.15482625354981</v>
+        <v>3.018751675924031</v>
       </c>
       <c r="E87" t="n">
-        <v>3.244328184911285</v>
+        <v>3.20658481022447</v>
       </c>
       <c r="F87" t="n">
-        <v>3.140721306832709</v>
+        <v>3.080868569951295</v>
       </c>
       <c r="G87" t="n">
-        <v>3.467976710334788</v>
+        <v>2.873256634440122</v>
       </c>
       <c r="H87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I87" t="n">
         <v>17</v>
       </c>
       <c r="J87" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K87" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="88">
@@ -3843,454 +3819,450 @@
         <v>2023</v>
       </c>
       <c r="D88" t="n">
-        <v>2.843814983420446</v>
+        <v>3.008783725666243</v>
       </c>
       <c r="E88" t="n">
-        <v>2.885501333576788</v>
+        <v>2.956556332004214</v>
       </c>
       <c r="F88" t="n">
-        <v>2.900151773036096</v>
+        <v>3.013902779496036</v>
       </c>
       <c r="G88" t="n">
-        <v>2.828723920426977</v>
+        <v>3.477734130300446</v>
       </c>
       <c r="H88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I88" t="n">
         <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K88" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>2023</v>
       </c>
       <c r="D89" t="n">
-        <v>2.727857286903971</v>
+        <v>2.449280883345847</v>
       </c>
       <c r="E89" t="n">
-        <v>2.711738349686599</v>
+        <v>1.978573447204863</v>
       </c>
       <c r="F89" t="n">
-        <v>2.765338512791215</v>
+        <v>2.347943604615446</v>
       </c>
       <c r="G89" t="n">
-        <v>2.582180980106744</v>
+        <v>6.125252940901976</v>
       </c>
       <c r="H89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I89" t="n">
         <v>19</v>
       </c>
       <c r="J89" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K89" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BOKL</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bank of Kathmandu Lumbini</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D90" t="n">
-        <v>2.170714854817327</v>
+        <v>8.732603832834487</v>
       </c>
       <c r="E90" t="n">
-        <v>2.157888528954967</v>
+        <v>9.114460921008389</v>
       </c>
       <c r="F90" t="n">
-        <v>2.174186671281856</v>
+        <v>8.60355308128571</v>
       </c>
       <c r="G90" t="n">
-        <v>2.122149442018437</v>
+        <v>11.51910826830028</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K90" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D91" t="n">
-        <v>2.010456855141315</v>
+        <v>8.078050316822438</v>
       </c>
       <c r="E91" t="n">
-        <v>1.984794169342448</v>
+        <v>9.17477996252685</v>
       </c>
       <c r="F91" t="n">
-        <v>2.013671855088419</v>
+        <v>8.155979011627776</v>
       </c>
       <c r="G91" t="n">
-        <v>1.922610383309073</v>
+        <v>11.63108148181514</v>
       </c>
       <c r="H91" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="K91" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CCBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Century Commercial Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D92" t="n">
-        <v>1.557783794684625</v>
+        <v>7.384292101452199</v>
       </c>
       <c r="E92" t="n">
-        <v>1.623338151356772</v>
+        <v>5.841699797973122</v>
       </c>
       <c r="F92" t="n">
-        <v>1.57918772406832</v>
+        <v>7.575126393494124</v>
       </c>
       <c r="G92" t="n">
-        <v>1.705937651625425</v>
+        <v>4.790617973521319</v>
       </c>
       <c r="H92" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I92" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="J92" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CIVIL</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Civil Bank</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D93" t="n">
-        <v>1.167841947097504</v>
+        <v>7.128468658018565</v>
       </c>
       <c r="E93" t="n">
-        <v>1.176955517492072</v>
+        <v>7.266457432117275</v>
       </c>
       <c r="F93" t="n">
-        <v>1.14135217597677</v>
+        <v>7.120274029434491</v>
       </c>
       <c r="G93" t="n">
-        <v>1.263797913634158</v>
+        <v>7.711793786106014</v>
       </c>
       <c r="H93" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I93" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="J93" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="K93" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C94" t="n">
         <v>2024</v>
       </c>
       <c r="D94" t="n">
-        <v>8.84754608291194</v>
+        <v>5.952713582557028</v>
       </c>
       <c r="E94" t="n">
-        <v>8.877728792354448</v>
+        <v>6.712455464631696</v>
       </c>
       <c r="F94" t="n">
-        <v>9.039174315808285</v>
+        <v>6.249778581848171</v>
       </c>
       <c r="G94" t="n">
-        <v>8.481024618878932</v>
+        <v>1.31661430239149</v>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C95" t="n">
         <v>2024</v>
       </c>
       <c r="D95" t="n">
-        <v>8.35379480575927</v>
+        <v>5.937994363195647</v>
       </c>
       <c r="E95" t="n">
-        <v>8.101008615676655</v>
+        <v>6.640458754482721</v>
       </c>
       <c r="F95" t="n">
-        <v>8.382323048969596</v>
+        <v>5.879385637893463</v>
       </c>
       <c r="G95" t="n">
-        <v>7.578920720042931</v>
+        <v>0.008652304966535662</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C96" t="n">
         <v>2024</v>
       </c>
       <c r="D96" t="n">
-        <v>7.519793839177693</v>
+        <v>5.742344444763205</v>
       </c>
       <c r="E96" t="n">
-        <v>7.748010384927221</v>
+        <v>6.074919930665831</v>
       </c>
       <c r="F96" t="n">
-        <v>7.408284516212195</v>
+        <v>5.805612357288279</v>
       </c>
       <c r="G96" t="n">
-        <v>8.421122067493773</v>
+        <v>5.481131969234581</v>
       </c>
       <c r="H96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>2024</v>
       </c>
       <c r="D97" t="n">
-        <v>6.458743508820867</v>
+        <v>5.237039398585947</v>
       </c>
       <c r="E97" t="n">
-        <v>6.611262855397154</v>
+        <v>5.257759993956108</v>
       </c>
       <c r="F97" t="n">
-        <v>6.480799157896647</v>
+        <v>5.383450102094859</v>
       </c>
       <c r="G97" t="n">
-        <v>6.833704455787104</v>
+        <v>0.9588105239055116</v>
       </c>
       <c r="H97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J97" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K97" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>HBL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>Himalayan Bank</t>
         </is>
       </c>
       <c r="C98" t="n">
         <v>2024</v>
       </c>
       <c r="D98" t="n">
-        <v>6.162606267211153</v>
-      </c>
-      <c r="E98" t="n">
-        <v>6.100629244039981</v>
-      </c>
+        <v>5.158975153787751</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="n">
-        <v>6.258605931550205</v>
+        <v>5.187302035934346</v>
       </c>
       <c r="G98" t="n">
-        <v>5.76330291258328</v>
+        <v>2.324110464221499</v>
       </c>
       <c r="H98" t="n">
-        <v>5</v>
-      </c>
-      <c r="I98" t="n">
-        <v>5</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K98" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>2024</v>
       </c>
       <c r="D99" t="n">
-        <v>5.332254308261677</v>
+        <v>4.935892895015005</v>
       </c>
       <c r="E99" t="n">
-        <v>5.350444112516106</v>
+        <v>4.630340586823031</v>
       </c>
       <c r="F99" t="n">
-        <v>5.253182815150405</v>
+        <v>4.996403406738096</v>
       </c>
       <c r="G99" t="n">
-        <v>5.569332746193247</v>
+        <v>6.451841758538755</v>
       </c>
       <c r="H99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K99" t="n">
         <v>6</v>
@@ -4299,742 +4271,742 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>HBL</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Himalayan Bank</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>2024</v>
       </c>
       <c r="D100" t="n">
-        <v>5.323172333710668</v>
+        <v>4.515649146679883</v>
       </c>
       <c r="E100" t="n">
-        <v>5.197941869553386</v>
+        <v>4.919374005318391</v>
       </c>
       <c r="F100" t="n">
-        <v>5.24423551633814</v>
+        <v>4.300024522082377</v>
       </c>
       <c r="G100" t="n">
-        <v>5.15839411243495</v>
+        <v>5.43817074132048</v>
       </c>
       <c r="H100" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I100" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J100" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>2024</v>
       </c>
       <c r="D101" t="n">
-        <v>5.314090359159658</v>
+        <v>4.312124208051948</v>
       </c>
       <c r="E101" t="n">
-        <v>5.332218197405447</v>
+        <v>4.786695281406732</v>
       </c>
       <c r="F101" t="n">
-        <v>5.2676057977155</v>
+        <v>4.259437136384445</v>
       </c>
       <c r="G101" t="n">
-        <v>5.474130477027551</v>
+        <v>5.780771988303435</v>
       </c>
       <c r="H101" t="n">
+        <v>12</v>
+      </c>
+      <c r="I101" t="n">
+        <v>11</v>
+      </c>
+      <c r="J101" t="n">
+        <v>12</v>
+      </c>
+      <c r="K101" t="n">
         <v>8</v>
-      </c>
-      <c r="I101" t="n">
-        <v>7</v>
-      </c>
-      <c r="J101" t="n">
-        <v>6</v>
-      </c>
-      <c r="K101" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C102" t="n">
         <v>2024</v>
       </c>
       <c r="D102" t="n">
-        <v>4.856018267743097</v>
+        <v>4.288953648465299</v>
       </c>
       <c r="E102" t="n">
-        <v>4.937988857640095</v>
+        <v>4.421031904829744</v>
       </c>
       <c r="F102" t="n">
-        <v>4.961194346040924</v>
+        <v>4.100367653324542</v>
       </c>
       <c r="G102" t="n">
-        <v>4.838022431366117</v>
+        <v>6.950428486165697</v>
       </c>
       <c r="H102" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I102" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J102" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C103" t="n">
         <v>2024</v>
       </c>
       <c r="D103" t="n">
-        <v>4.84855807436191</v>
+        <v>4.27625633495574</v>
       </c>
       <c r="E103" t="n">
-        <v>4.897751611444809</v>
+        <v>4.815082041919436</v>
       </c>
       <c r="F103" t="n">
-        <v>4.865115426762582</v>
+        <v>3.952567109873854</v>
       </c>
       <c r="G103" t="n">
-        <v>4.947308931363443</v>
+        <v>4.212415025356322</v>
       </c>
       <c r="H103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I103" t="n">
         <v>10</v>
       </c>
       <c r="J103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K103" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>2024</v>
       </c>
       <c r="D104" t="n">
-        <v>4.632780089716934</v>
+        <v>3.872139395868512</v>
       </c>
       <c r="E104" t="n">
-        <v>4.648584741527735</v>
+        <v>4.518550844208861</v>
       </c>
       <c r="F104" t="n">
-        <v>4.592254373125439</v>
+        <v>3.72696045731968</v>
       </c>
       <c r="G104" t="n">
-        <v>4.772414875087136</v>
+        <v>6.583803485696482</v>
       </c>
       <c r="H104" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I104" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J104" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K104" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NMB Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>2024</v>
       </c>
       <c r="D105" t="n">
-        <v>4.520228476531204</v>
+        <v>3.391531852809234</v>
       </c>
       <c r="E105" t="n">
-        <v>4.413886766827944</v>
+        <v>3.923299673826149</v>
       </c>
       <c r="F105" t="n">
-        <v>4.480687316661493</v>
+        <v>3.480511023139868</v>
       </c>
       <c r="G105" t="n">
-        <v>4.315479639372378</v>
+        <v>4.499649027976412</v>
       </c>
       <c r="H105" t="n">
+        <v>16</v>
+      </c>
+      <c r="I105" t="n">
+        <v>15</v>
+      </c>
+      <c r="J105" t="n">
+        <v>16</v>
+      </c>
+      <c r="K105" t="n">
         <v>12</v>
-      </c>
-      <c r="I105" t="n">
-        <v>12</v>
-      </c>
-      <c r="J105" t="n">
-        <v>12</v>
-      </c>
-      <c r="K105" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C106" t="n">
         <v>2024</v>
       </c>
       <c r="D106" t="n">
-        <v>4.350590166167699</v>
+        <v>3.2293968149005</v>
       </c>
       <c r="E106" t="n">
-        <v>4.365432131772843</v>
+        <v>3.690728181572493</v>
       </c>
       <c r="F106" t="n">
-        <v>4.28607567746053</v>
+        <v>3.34001065998233</v>
       </c>
       <c r="G106" t="n">
-        <v>4.544036397931223</v>
+        <v>2.478819682961528</v>
       </c>
       <c r="H106" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I106" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J106" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K106" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C107" t="n">
         <v>2024</v>
       </c>
       <c r="D107" t="n">
-        <v>4.295206339218237</v>
+        <v>3.028226464094266</v>
       </c>
       <c r="E107" t="n">
-        <v>4.280934133194132</v>
+        <v>3.14556123442731</v>
       </c>
       <c r="F107" t="n">
-        <v>4.388235840618547</v>
+        <v>3.097821914670693</v>
       </c>
       <c r="G107" t="n">
-        <v>4.036290962380841</v>
+        <v>3.753279805407597</v>
       </c>
       <c r="H107" t="n">
+        <v>18</v>
+      </c>
+      <c r="I107" t="n">
+        <v>17</v>
+      </c>
+      <c r="J107" t="n">
+        <v>18</v>
+      </c>
+      <c r="K107" t="n">
         <v>14</v>
-      </c>
-      <c r="I107" t="n">
-        <v>15</v>
-      </c>
-      <c r="J107" t="n">
-        <v>13</v>
-      </c>
-      <c r="K107" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C108" t="n">
         <v>2024</v>
       </c>
       <c r="D108" t="n">
-        <v>4.188087692951415</v>
+        <v>2.749786012546972</v>
       </c>
       <c r="E108" t="n">
-        <v>4.286986866987473</v>
+        <v>3.136299257875655</v>
       </c>
       <c r="F108" t="n">
-        <v>4.075044877035296</v>
+        <v>2.800104073767823</v>
       </c>
       <c r="G108" t="n">
-        <v>4.731053589606907</v>
+        <v>1.961689620612381</v>
       </c>
       <c r="H108" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I108" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J108" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K108" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C109" t="n">
         <v>2024</v>
       </c>
       <c r="D109" t="n">
-        <v>3.696039286027058</v>
+        <v>2.047561374595376</v>
       </c>
       <c r="E109" t="n">
-        <v>3.658867748662185</v>
+        <v>1.930044730430207</v>
       </c>
       <c r="F109" t="n">
-        <v>3.731138010210296</v>
+        <v>1.985330811815066</v>
       </c>
       <c r="G109" t="n">
-        <v>3.509291135313802</v>
+        <v>6.147209303198538</v>
       </c>
       <c r="H109" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I109" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J109" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K109" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CZBIL</t>
+          <t>GIBL</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Citizens Bank International</t>
+          <t>Global IME Bank</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D110" t="n">
-        <v>3.327976049535684</v>
+        <v>8.871317824420158</v>
       </c>
       <c r="E110" t="n">
-        <v>3.272093472208516</v>
+        <v>9.263748678774771</v>
       </c>
       <c r="F110" t="n">
-        <v>3.298864732562852</v>
+        <v>8.545389937331324</v>
       </c>
       <c r="G110" t="n">
-        <v>3.240086216886458</v>
+        <v>9.60939984553178</v>
       </c>
       <c r="H110" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J110" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="K110" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SBI</t>
+          <t>NABIL</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nepal SBI Bank</t>
+          <t>Nabil Bank</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D111" t="n">
-        <v>2.983104283772782</v>
+        <v>8.210004449838468</v>
       </c>
       <c r="E111" t="n">
-        <v>2.9129245547156</v>
+        <v>9.283583631350799</v>
       </c>
       <c r="F111" t="n">
-        <v>3.029573919412965</v>
+        <v>8.141846393131868</v>
       </c>
       <c r="G111" t="n">
-        <v>2.677251827830084</v>
+        <v>11.21056895794527</v>
       </c>
       <c r="H111" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I111" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MBL</t>
+          <t>RBB</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Machhapuchchhre Bank</t>
+          <t>Rastriya Banijya Bank</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D112" t="n">
-        <v>2.875012568804066</v>
+        <v>7.550645889270577</v>
       </c>
       <c r="E112" t="n">
-        <v>2.826738081498761</v>
+        <v>6.603379650398045</v>
       </c>
       <c r="F112" t="n">
-        <v>2.797411634821995</v>
+        <v>7.766103410948704</v>
       </c>
       <c r="G112" t="n">
-        <v>2.922567038264538</v>
+        <v>5.36852785728348</v>
       </c>
       <c r="H112" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I112" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="K112" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SCB</t>
+          <t>NIMB</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Standard Chartered Bank Nepal</t>
+          <t>Nepal Investment Mega Bank</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D113" t="n">
-        <v>2.114397200156988</v>
+        <v>7.257450862187468</v>
       </c>
       <c r="E113" t="n">
-        <v>2.17856696164952</v>
+        <v>7.300015413757889</v>
       </c>
       <c r="F113" t="n">
-        <v>2.160192745646107</v>
+        <v>7.330518956638102</v>
       </c>
       <c r="G113" t="n">
-        <v>2.186264844155311</v>
+        <v>8.200975269940788</v>
       </c>
       <c r="H113" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I113" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="K113" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>GIBL</t>
+          <t>LLBS</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Global IME Bank</t>
+          <t>Laxmi Sunrise Bank</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>2025</v>
       </c>
       <c r="D114" t="n">
-        <v>8.875793577857257</v>
+        <v>5.719110090066102</v>
       </c>
       <c r="E114" t="n">
-        <v>8.669504081837243</v>
+        <v>6.396933372806118</v>
       </c>
       <c r="F114" t="n">
-        <v>9.111495093800478</v>
+        <v>5.696429747489375</v>
       </c>
       <c r="G114" t="n">
-        <v>7.720507231884698</v>
+        <v>7.689412869322915</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K114" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NABIL</t>
+          <t>KBL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nabil Bank</t>
+          <t>Kumari Bank</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>2025</v>
       </c>
       <c r="D115" t="n">
-        <v>8.374939361160409</v>
+        <v>5.694561199951017</v>
       </c>
       <c r="E115" t="n">
-        <v>8.634751213177395</v>
+        <v>5.880222817731349</v>
       </c>
       <c r="F115" t="n">
-        <v>8.241237977695858</v>
+        <v>5.65895753546133</v>
       </c>
       <c r="G115" t="n">
-        <v>9.436363821255336</v>
+        <v>3.444679175563734</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K115" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NIMB</t>
+          <t>PRVU</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Nepal Investment Mega Bank</t>
+          <t>Prabhu Bank</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>2025</v>
       </c>
       <c r="D116" t="n">
-        <v>7.49774770024376</v>
+        <v>5.229446327101471</v>
       </c>
       <c r="E116" t="n">
-        <v>7.323486482832493</v>
+        <v>5.092650671538883</v>
       </c>
       <c r="F116" t="n">
-        <v>7.696855304034875</v>
+        <v>5.31053882688165</v>
       </c>
       <c r="G116" t="n">
-        <v>6.521915983363445</v>
+        <v>1.651314494268017</v>
       </c>
       <c r="H116" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I116" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J116" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>NBL</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NIC Asia Bank</t>
+          <t>Nepal Bank Limited</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>2025</v>
       </c>
       <c r="D117" t="n">
-        <v>6.45182187698677</v>
+        <v>5.139627509557921</v>
       </c>
       <c r="E117" t="n">
-        <v>6.301869867429579</v>
+        <v>4.980700230409456</v>
       </c>
       <c r="F117" t="n">
-        <v>6.583963581949262</v>
+        <v>5.153852975310474</v>
       </c>
       <c r="G117" t="n">
-        <v>5.706697670950094</v>
+        <v>5.826688928263142</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J117" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K117" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RBB</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Rastriya Banijya Bank</t>
+          <t>NIC Asia Bank</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>2025</v>
       </c>
       <c r="D118" t="n">
-        <v>6.170698710087591</v>
+        <v>4.832868301103656</v>
       </c>
       <c r="E118" t="n">
-        <v>6.02728051138466</v>
+        <v>5.157478446184601</v>
       </c>
       <c r="F118" t="n">
-        <v>6.222117377284064</v>
+        <v>4.95169081432107</v>
       </c>
       <c r="G118" t="n">
-        <v>5.638904048296177</v>
+        <v>-7.312934441869974</v>
       </c>
       <c r="H118" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K118" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119">
@@ -5052,574 +5024,414 @@
         <v>2025</v>
       </c>
       <c r="D119" t="n">
-        <v>5.324617410352444</v>
-      </c>
-      <c r="E119" t="n">
-        <v>5.200863671326646</v>
-      </c>
+        <v>4.787099068122806</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="n">
-        <v>5.207270395732029</v>
+        <v>4.797937186038117</v>
       </c>
       <c r="G119" t="n">
-        <v>5.255531112188277</v>
+        <v>0.2455779685914618</v>
       </c>
       <c r="H119" t="n">
-        <v>6</v>
-      </c>
-      <c r="I119" t="n">
-        <v>8</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K119" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KBL</t>
+          <t>EBL</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kumari Bank</t>
+          <t>Everest Bank</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>2025</v>
       </c>
       <c r="D120" t="n">
-        <v>5.321001678302293</v>
+        <v>4.688346536514886</v>
       </c>
       <c r="E120" t="n">
-        <v>5.413887474405168</v>
+        <v>4.821198172266867</v>
       </c>
       <c r="F120" t="n">
-        <v>5.17141210910107</v>
+        <v>4.637463064621194</v>
       </c>
       <c r="G120" t="n">
-        <v>5.946009158918421</v>
+        <v>9.161896324564989</v>
       </c>
       <c r="H120" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I120" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J120" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K120" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PRVU</t>
+          <t>ADBL</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Prabhu Bank</t>
+          <t>Agriculture Development Bank</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>2025</v>
       </c>
       <c r="D121" t="n">
-        <v>5.310154482151843</v>
+        <v>4.661128955246157</v>
       </c>
       <c r="E121" t="n">
-        <v>5.474888937054572</v>
+        <v>4.802636292457558</v>
       </c>
       <c r="F121" t="n">
-        <v>5.289891607200729</v>
+        <v>4.552736492883127</v>
       </c>
       <c r="G121" t="n">
-        <v>5.827539803330701</v>
+        <v>7.065444550452046</v>
       </c>
       <c r="H121" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I121" t="n">
+        <v>13</v>
+      </c>
+      <c r="J121" t="n">
+        <v>12</v>
+      </c>
+      <c r="K121" t="n">
         <v>6</v>
-      </c>
-      <c r="J121" t="n">
-        <v>6</v>
-      </c>
-      <c r="K121" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NBL</t>
+          <t>NMB</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Nepal Bank Limited</t>
+          <t>NMB Bank</t>
         </is>
       </c>
       <c r="C122" t="n">
         <v>2025</v>
       </c>
       <c r="D122" t="n">
-        <v>4.86654935624904</v>
+        <v>4.533029717015078</v>
       </c>
       <c r="E122" t="n">
-        <v>4.885482001380182</v>
+        <v>5.160423951663316</v>
       </c>
       <c r="F122" t="n">
-        <v>4.818418830754469</v>
+        <v>4.359792196529442</v>
       </c>
       <c r="G122" t="n">
-        <v>5.03638822695949</v>
+        <v>5.403813244892705</v>
       </c>
       <c r="H122" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I122" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J122" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K122" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LLBS</t>
+          <t>SBL</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Laxmi Sunrise Bank</t>
+          <t>Siddhartha Bank</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>2025</v>
       </c>
       <c r="D123" t="n">
-        <v>4.847566762985752</v>
+        <v>4.368244130149407</v>
       </c>
       <c r="E123" t="n">
-        <v>4.76778128665118</v>
+        <v>4.844192992645177</v>
       </c>
       <c r="F123" t="n">
-        <v>4.887961065280292</v>
+        <v>4.350401446493962</v>
       </c>
       <c r="G123" t="n">
-        <v>4.523359987525974</v>
+        <v>6.372930958763042</v>
       </c>
       <c r="H123" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I123" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J123" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K123" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>SBL</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Siddhartha Bank</t>
+          <t>Prime Commercial Bank</t>
         </is>
       </c>
       <c r="C124" t="n">
         <v>2025</v>
       </c>
       <c r="D124" t="n">
-        <v>4.629040957204798</v>
+        <v>4.080478540327148</v>
       </c>
       <c r="E124" t="n">
-        <v>4.709847576051791</v>
+        <v>4.72318150805155</v>
       </c>
       <c r="F124" t="n">
-        <v>4.49890451213906</v>
+        <v>4.087182959778087</v>
       </c>
       <c r="G124" t="n">
-        <v>5.172653408493863</v>
+        <v>6.059015946572169</v>
       </c>
       <c r="H124" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I124" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J124" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K124" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NMB</t>
+          <t>SANIMA</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>NMB Bank</t>
+          <t>Sanima Bank</t>
         </is>
       </c>
       <c r="C125" t="n">
         <v>2025</v>
       </c>
       <c r="D125" t="n">
-        <v>4.512433598587454</v>
+        <v>3.397935668955741</v>
       </c>
       <c r="E125" t="n">
-        <v>4.591204666988975</v>
+        <v>3.985479209142802</v>
       </c>
       <c r="F125" t="n">
-        <v>4.632263954619574</v>
+        <v>3.475627861768414</v>
       </c>
       <c r="G125" t="n">
-        <v>4.447600614210221</v>
+        <v>4.869648509078794</v>
       </c>
       <c r="H125" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I125" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J125" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K125" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>CZBIL</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Prime Commercial Bank</t>
+          <t>Citizens Bank International</t>
         </is>
       </c>
       <c r="C126" t="n">
         <v>2025</v>
       </c>
       <c r="D126" t="n">
-        <v>4.348821723318157</v>
+        <v>3.163685981420422</v>
       </c>
       <c r="E126" t="n">
-        <v>4.395238464582945</v>
+        <v>3.814265604369814</v>
       </c>
       <c r="F126" t="n">
-        <v>4.358643191397759</v>
+        <v>3.282351762017344</v>
       </c>
       <c r="G126" t="n">
-        <v>4.45709172138177</v>
+        <v>2.436433298502264</v>
       </c>
       <c r="H126" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I126" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J126" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K126" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ADBL</t>
+          <t>SBI</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Agriculture Development Bank</t>
+          <t>Nepal SBI Bank</t>
         </is>
       </c>
       <c r="C127" t="n">
         <v>2025</v>
       </c>
       <c r="D127" t="n">
-        <v>4.285320429187394</v>
+        <v>3.001687699934269</v>
       </c>
       <c r="E127" t="n">
-        <v>4.41826193349927</v>
+        <v>3.048592975176342</v>
       </c>
       <c r="F127" t="n">
-        <v>4.190876851695145</v>
+        <v>3.097712793359888</v>
       </c>
       <c r="G127" t="n">
-        <v>4.891309874480108</v>
+        <v>3.428134417639665</v>
       </c>
       <c r="H127" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I127" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J127" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K127" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EBL</t>
+          <t>MBL</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Everest Bank</t>
+          <t>Machhapuchchhre Bank</t>
         </is>
       </c>
       <c r="C128" t="n">
         <v>2025</v>
       </c>
       <c r="D128" t="n">
-        <v>4.179786249973636</v>
+        <v>2.803601427011651</v>
       </c>
       <c r="E128" t="n">
-        <v>4.309453816484865</v>
+        <v>3.194790338671555</v>
       </c>
       <c r="F128" t="n">
-        <v>4.21461521314898</v>
+        <v>2.858289948888108</v>
       </c>
       <c r="G128" t="n">
-        <v>4.4645490198737</v>
+        <v>3.565717141429285</v>
       </c>
       <c r="H128" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I128" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J128" t="n">
+        <v>19</v>
+      </c>
+      <c r="K128" t="n">
         <v>14</v>
-      </c>
-      <c r="K128" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SANIMA</t>
+          <t>SCB</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Sanima Bank</t>
+          <t>Standard Chartered Bank Nepal</t>
         </is>
       </c>
       <c r="C129" t="n">
         <v>2025</v>
       </c>
       <c r="D129" t="n">
-        <v>3.692566356215896</v>
+        <v>2.00972982180559</v>
       </c>
       <c r="E129" t="n">
-        <v>3.706931780940431</v>
+        <v>1.646526042603114</v>
       </c>
       <c r="F129" t="n">
-        <v>3.61118679709307</v>
+        <v>1.945175690108427</v>
       </c>
       <c r="G129" t="n">
-        <v>3.929657337134296</v>
+        <v>5.702754683264428</v>
       </c>
       <c r="H129" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I129" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J129" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K129" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>CZBIL</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Citizens Bank International</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D130" t="n">
-        <v>3.3386012540564</v>
-      </c>
-      <c r="E130" t="n">
-        <v>3.283651487425435</v>
-      </c>
-      <c r="F130" t="n">
-        <v>3.386700964602919</v>
-      </c>
-      <c r="G130" t="n">
-        <v>3.066305552636663</v>
-      </c>
-      <c r="H130" t="n">
-        <v>17</v>
-      </c>
-      <c r="I130" t="n">
-        <v>17</v>
-      </c>
-      <c r="J130" t="n">
-        <v>17</v>
-      </c>
-      <c r="K130" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>SBI</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Nepal SBI Bank</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D131" t="n">
-        <v>2.976048788277797</v>
-      </c>
-      <c r="E131" t="n">
-        <v>2.927066698672661</v>
-      </c>
-      <c r="F131" t="n">
-        <v>2.946615170467516</v>
-      </c>
-      <c r="G131" t="n">
-        <v>2.907668475626497</v>
-      </c>
-      <c r="H131" t="n">
-        <v>18</v>
-      </c>
-      <c r="I131" t="n">
-        <v>18</v>
-      </c>
-      <c r="J131" t="n">
-        <v>18</v>
-      </c>
-      <c r="K131" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>MBL</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Machhapuchchhre Bank</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D132" t="n">
-        <v>2.881663116218667</v>
-      </c>
-      <c r="E132" t="n">
-        <v>2.892873832718812</v>
-      </c>
-      <c r="F132" t="n">
-        <v>2.835659836125506</v>
-      </c>
-      <c r="G132" t="n">
-        <v>3.024612474704504</v>
-      </c>
-      <c r="H132" t="n">
-        <v>19</v>
-      </c>
-      <c r="I132" t="n">
-        <v>19</v>
-      </c>
-      <c r="J132" t="n">
-        <v>19</v>
-      </c>
-      <c r="K132" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>SCB</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Standard Chartered Bank Nepal</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D133" t="n">
-        <v>2.114826610582645</v>
-      </c>
-      <c r="E133" t="n">
-        <v>2.065674215155697</v>
-      </c>
-      <c r="F133" t="n">
-        <v>2.093910165877337</v>
-      </c>
-      <c r="G133" t="n">
-        <v>2.025334476785769</v>
-      </c>
-      <c r="H133" t="n">
-        <v>20</v>
-      </c>
-      <c r="I133" t="n">
-        <v>20</v>
-      </c>
-      <c r="J133" t="n">
-        <v>20</v>
-      </c>
-      <c r="K133" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -5718,40 +5530,40 @@
         <v>2020</v>
       </c>
       <c r="B2" t="n">
-        <v>513</v>
+        <v>482.5</v>
       </c>
       <c r="C2" t="n">
-        <v>29.47</v>
+        <v>27.28</v>
       </c>
       <c r="D2" t="n">
-        <v>35.25</v>
+        <v>32.66</v>
       </c>
       <c r="E2" t="n">
-        <v>59.73</v>
+        <v>56.94</v>
       </c>
       <c r="F2" t="n">
-        <v>511.4</v>
+        <v>477.8</v>
       </c>
       <c r="G2" t="n">
-        <v>29.13</v>
+        <v>26.36</v>
       </c>
       <c r="H2" t="n">
-        <v>34.95</v>
+        <v>31.87</v>
       </c>
       <c r="I2" t="n">
-        <v>59.71</v>
+        <v>55.66</v>
       </c>
       <c r="J2" t="n">
-        <v>513.3</v>
+        <v>484.4</v>
       </c>
       <c r="K2" t="n">
-        <v>29.57</v>
+        <v>27.8</v>
       </c>
       <c r="L2" t="n">
-        <v>35.34</v>
+        <v>33.34</v>
       </c>
       <c r="M2" t="n">
-        <v>59.64</v>
+        <v>56.64</v>
       </c>
       <c r="N2" t="n">
         <v>23</v>
@@ -5767,40 +5579,40 @@
         <v>2021</v>
       </c>
       <c r="B3" t="n">
-        <v>513.6</v>
+        <v>484.6</v>
       </c>
       <c r="C3" t="n">
-        <v>29.54</v>
+        <v>27.84</v>
       </c>
       <c r="D3" t="n">
-        <v>35.36</v>
+        <v>32.83</v>
       </c>
       <c r="E3" t="n">
-        <v>59.81</v>
+        <v>56.89</v>
       </c>
       <c r="F3" t="n">
-        <v>514</v>
+        <v>484.2</v>
       </c>
       <c r="G3" t="n">
-        <v>29.63</v>
+        <v>27.78</v>
       </c>
       <c r="H3" t="n">
-        <v>35.26</v>
+        <v>32.89</v>
       </c>
       <c r="I3" t="n">
-        <v>59.88</v>
+        <v>55.8</v>
       </c>
       <c r="J3" t="n">
-        <v>514.4</v>
+        <v>486.6</v>
       </c>
       <c r="K3" t="n">
-        <v>29.58</v>
+        <v>28.58</v>
       </c>
       <c r="L3" t="n">
-        <v>35.35</v>
+        <v>33.53</v>
       </c>
       <c r="M3" t="n">
-        <v>59.67</v>
+        <v>56.27</v>
       </c>
       <c r="N3" t="n">
         <v>23</v>
@@ -5816,43 +5628,43 @@
         <v>2022</v>
       </c>
       <c r="B4" t="n">
-        <v>514.1</v>
+        <v>525.3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.6</v>
+        <v>29.56</v>
       </c>
       <c r="D4" t="n">
-        <v>35.44</v>
+        <v>34.88</v>
       </c>
       <c r="E4" t="n">
-        <v>59.87</v>
+        <v>59.81</v>
       </c>
       <c r="F4" t="n">
-        <v>514.9</v>
+        <v>558.6</v>
       </c>
       <c r="G4" t="n">
-        <v>29.77</v>
+        <v>31.72</v>
       </c>
       <c r="H4" t="n">
-        <v>35.69</v>
+        <v>37.13</v>
       </c>
       <c r="I4" t="n">
-        <v>59.8</v>
+        <v>62.64</v>
       </c>
       <c r="J4" t="n">
-        <v>512.7</v>
+        <v>546</v>
       </c>
       <c r="K4" t="n">
-        <v>29.39</v>
+        <v>30.78</v>
       </c>
       <c r="L4" t="n">
-        <v>35.32</v>
+        <v>36.02</v>
       </c>
       <c r="M4" t="n">
-        <v>59.67</v>
+        <v>60.53</v>
       </c>
       <c r="N4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -5865,43 +5677,43 @@
         <v>2023</v>
       </c>
       <c r="B5" t="n">
-        <v>514.4</v>
+        <v>554</v>
       </c>
       <c r="C5" t="n">
-        <v>29.63</v>
+        <v>29.91</v>
       </c>
       <c r="D5" t="n">
-        <v>35.49</v>
+        <v>36.06</v>
       </c>
       <c r="E5" t="n">
-        <v>59.91</v>
+        <v>63.61</v>
       </c>
       <c r="F5" t="n">
-        <v>512.2</v>
+        <v>598</v>
       </c>
       <c r="G5" t="n">
-        <v>29.44</v>
+        <v>32.83</v>
       </c>
       <c r="H5" t="n">
-        <v>35.26</v>
+        <v>39.74</v>
       </c>
       <c r="I5" t="n">
-        <v>59.65</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>514</v>
+        <v>557.1</v>
       </c>
       <c r="K5" t="n">
-        <v>29.68</v>
+        <v>29.96</v>
       </c>
       <c r="L5" t="n">
-        <v>35.65</v>
+        <v>36.27</v>
       </c>
       <c r="M5" t="n">
-        <v>59.84</v>
+        <v>64.58</v>
       </c>
       <c r="N5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -5914,40 +5726,40 @@
         <v>2024</v>
       </c>
       <c r="B6" t="n">
-        <v>559.6</v>
+        <v>562.4</v>
       </c>
       <c r="C6" t="n">
-        <v>31.18</v>
+        <v>31.32</v>
       </c>
       <c r="D6" t="n">
-        <v>37.34</v>
+        <v>37.28</v>
       </c>
       <c r="E6" t="n">
-        <v>63.02</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34</v>
+        <v>32.27</v>
       </c>
       <c r="H6" t="n">
-        <v>37.44</v>
+        <v>38.91</v>
       </c>
       <c r="I6" t="n">
-        <v>63.15</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>561</v>
+        <v>564.4</v>
       </c>
       <c r="K6" t="n">
-        <v>31.31</v>
+        <v>31.45</v>
       </c>
       <c r="L6" t="n">
-        <v>37.57</v>
+        <v>37.7</v>
       </c>
       <c r="M6" t="n">
-        <v>63.16</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="N6" t="n">
         <v>20</v>
@@ -5963,40 +5775,40 @@
         <v>2025</v>
       </c>
       <c r="B7" t="n">
-        <v>559.8</v>
+        <v>563.4</v>
       </c>
       <c r="C7" t="n">
-        <v>31.2</v>
+        <v>31.89</v>
       </c>
       <c r="D7" t="n">
-        <v>37.37</v>
+        <v>37.61</v>
       </c>
       <c r="E7" t="n">
-        <v>63.04</v>
+        <v>63.29</v>
       </c>
       <c r="F7" t="n">
-        <v>558.7</v>
+        <v>593.1</v>
       </c>
       <c r="G7" t="n">
-        <v>30.93</v>
+        <v>32.45</v>
       </c>
       <c r="H7" t="n">
-        <v>36.96</v>
+        <v>38.85</v>
       </c>
       <c r="I7" t="n">
-        <v>62.7</v>
+        <v>65.12</v>
       </c>
       <c r="J7" t="n">
-        <v>562.8</v>
+        <v>561.4</v>
       </c>
       <c r="K7" t="n">
-        <v>31.63</v>
+        <v>31.78</v>
       </c>
       <c r="L7" t="n">
-        <v>37.86</v>
+        <v>37.48</v>
       </c>
       <c r="M7" t="n">
-        <v>63.23</v>
+        <v>63.35</v>
       </c>
       <c r="N7" t="n">
         <v>20</v>
